--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\KEI\Desktop\02. 에디터 업무\05. 과제명 영문화\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\KEI\Documents\Messenger Download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2FF1D5F-B216-4367-AA61-7775D54175F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1783F718-4EE0-4490-9355-103088090214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3C5D53B1-B2EF-4151-8264-D443F1D8BF97}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3C5D53B1-B2EF-4151-8264-D443F1D8BF97}"/>
   </bookViews>
   <sheets>
-    <sheet name="총괄" sheetId="1" r:id="rId1"/>
+    <sheet name="List" sheetId="1" r:id="rId1"/>
     <sheet name="DB1" sheetId="3" r:id="rId2"/>
     <sheet name="DB2" sheetId="4" r:id="rId3"/>
   </sheets>
@@ -8538,11 +8538,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12419,15 +12419,15 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.25" thickBot="1"/>
     <row r="2" spans="1:8" ht="42" thickBot="1">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="52" t="s">
         <v>1815</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
     </row>
     <row r="3" spans="1:8" ht="41.25">
       <c r="B3" s="4"/>
@@ -12932,7 +12932,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="33">
+    <row r="16" spans="1:8">
       <c r="A16" s="18" t="s">
         <v>895</v>
       </c>
@@ -13362,7 +13362,7 @@
         <v>45777</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="33">
+    <row r="26" spans="1:8">
       <c r="A26" s="18" t="s">
         <v>904</v>
       </c>
@@ -16965,7 +16965,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="33">
+    <row r="110" spans="1:8">
       <c r="A110" s="18" t="s">
         <v>864</v>
       </c>
@@ -17051,7 +17051,7 @@
         <v>45961</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="33">
+    <row r="112" spans="1:8">
       <c r="A112" s="18" t="s">
         <v>870</v>
       </c>
@@ -17180,7 +17180,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="33">
+    <row r="115" spans="1:8">
       <c r="A115" s="18" t="s">
         <v>875</v>
       </c>
@@ -17825,7 +17825,7 @@
         <v>46535</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="33">
+    <row r="130" spans="1:8">
       <c r="A130" s="18" t="s">
         <v>764</v>
       </c>
@@ -17868,7 +17868,7 @@
         <v>45903</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="33">
+    <row r="131" spans="1:8">
       <c r="A131" s="18" t="s">
         <v>767</v>
       </c>
@@ -21093,7 +21093,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="33">
+    <row r="206" spans="1:8">
       <c r="A206" s="18" t="s">
         <v>964</v>
       </c>
@@ -21781,7 +21781,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="33">
+    <row r="222" spans="1:8">
       <c r="A222" s="23" t="s">
         <v>790</v>
       </c>
@@ -22383,7 +22383,7 @@
         <v>46151</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="33">
+    <row r="236" spans="1:8">
       <c r="A236" s="23" t="s">
         <v>976</v>
       </c>
@@ -22899,7 +22899,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="248" spans="1:8" ht="33">
+    <row r="248" spans="1:8">
       <c r="A248" s="18" t="s">
         <v>809</v>
       </c>
@@ -23372,7 +23372,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="259" spans="1:8" ht="33">
+    <row r="259" spans="1:8">
       <c r="A259" s="18" t="s">
         <v>2229</v>
       </c>
@@ -23587,7 +23587,7 @@
         <v>45808</v>
       </c>
     </row>
-    <row r="264" spans="1:8" ht="33">
+    <row r="264" spans="1:8">
       <c r="A264" s="18" t="s">
         <v>752</v>
       </c>
@@ -25436,7 +25436,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="307" spans="1:8" ht="33">
+    <row r="307" spans="1:8">
       <c r="A307" s="23" t="s">
         <v>1914</v>
       </c>
@@ -26038,7 +26038,7 @@
         <v>46326</v>
       </c>
     </row>
-    <row r="321" spans="1:8" ht="33">
+    <row r="321" spans="1:8">
       <c r="A321" s="23" t="s">
         <v>1929</v>
       </c>
@@ -26167,7 +26167,7 @@
         <v>46326</v>
       </c>
     </row>
-    <row r="324" spans="1:8" ht="33">
+    <row r="324" spans="1:8">
       <c r="A324" s="23" t="s">
         <v>1933</v>
       </c>
@@ -26210,7 +26210,7 @@
         <v>46326</v>
       </c>
     </row>
-    <row r="325" spans="1:8" ht="33">
+    <row r="325" spans="1:8">
       <c r="A325" s="23" t="s">
         <v>1934</v>
       </c>
@@ -26683,7 +26683,7 @@
         <v>46387</v>
       </c>
     </row>
-    <row r="336" spans="1:8" ht="33">
+    <row r="336" spans="1:8">
       <c r="A336" s="23" t="s">
         <v>1948</v>
       </c>
@@ -27113,7 +27113,7 @@
         <v>46319</v>
       </c>
     </row>
-    <row r="346" spans="1:8" ht="33">
+    <row r="346" spans="1:8">
       <c r="A346" s="23" t="s">
         <v>1951</v>
       </c>
@@ -50341,10 +50341,10 @@
       <c r="B56" s="7" t="s">
         <v>1115</v>
       </c>
-      <c r="F56" s="52" t="s">
+      <c r="F56" s="51" t="s">
         <v>2387</v>
       </c>
-      <c r="G56" s="52" t="s">
+      <c r="G56" s="51" t="s">
         <v>2386</v>
       </c>
     </row>
